--- a/audio/※bgmリスト.xlsx
+++ b/audio/※bgmリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\LS210D597\share\※２．2026年01月01日～\1．ナレッジ\０６－4.2．ClaudeCode\いしちゃんのホームページ\6516mjnt-design.github.io\audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3090A87-4700-4B2A-A1C5-C920159D96AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C19E519-8F79-4FEA-A52D-42724CE7F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2B91B0EB-8191-4BBC-A706-21B28F855E19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2B91B0EB-8191-4BBC-A706-21B28F855E19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,116 +20,200 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">https://dova-s.jp/
 </t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>切ない</t>
-    <rPh sb="0" eb="1">
-      <t>セツ</t>
+    <t>Escort.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm2</t>
+  </si>
+  <si>
+    <t>bgm3</t>
+  </si>
+  <si>
+    <t>bgm4</t>
+  </si>
+  <si>
+    <t>bgm5</t>
+  </si>
+  <si>
+    <t>神隠しの真相.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You_and_Me.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10℃.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野良猫は宇宙を目指した.mp3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青空空港</t>
+  </si>
+  <si>
+    <t>いつもの風景</t>
+  </si>
+  <si>
+    <t>Parade</t>
+  </si>
+  <si>
+    <t>コールドフィッシュ</t>
+  </si>
+  <si>
+    <t>ながれぼし</t>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>春よ、強く美しく</t>
+  </si>
+  <si>
+    <t>orchestral_mission</t>
+  </si>
+  <si>
+    <t>人狼の為の子守唄</t>
+  </si>
+  <si>
+    <t>木漏れ日</t>
+  </si>
+  <si>
+    <t>ワスレナグサ</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローファイ少女は今日も寝不足</t>
+  </si>
+  <si>
+    <t>夏の思い出</t>
+  </si>
+  <si>
+    <t>ゆりかご</t>
+  </si>
+  <si>
+    <t>ひらひらり</t>
+  </si>
+  <si>
+    <t>全てが終わる夜に</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>トップ画面</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Escort.mp3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bgm1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bgm2</t>
-  </si>
-  <si>
-    <t>bgm3</t>
-  </si>
-  <si>
-    <t>bgm4</t>
-  </si>
-  <si>
-    <t>bgm5</t>
-  </si>
-  <si>
-    <t>神隠しの真相.mp3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>You_and_Me.mp3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>10℃.mp3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>野良猫は宇宙を目指した.mp3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>青空空港</t>
-  </si>
-  <si>
-    <t>いつもの風景</t>
-  </si>
-  <si>
-    <t>Parade</t>
-  </si>
-  <si>
-    <t>コールドフィッシュ</t>
-  </si>
-  <si>
-    <t>ながれぼし</t>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>お釈迦様の教え</t>
+    <rPh sb="1" eb="4">
+      <t>シャカサマ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm101</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある冬の寒い夜に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追憶</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堕ちる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手紙のさよなら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ムスカリの花</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -550,117 +634,237 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B01FD5-C79C-4FB1-933B-034233EA6D74}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="19.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.796875" style="1"/>
-    <col min="3" max="3" width="32.59765625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="5.9140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.4140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.9140625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="E4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="1">
+        <v>101</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1">
+        <v>102</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="3" t="s">
+      <c r="F6" s="1">
+        <v>103</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
+      <c r="F7" s="1">
+        <v>104</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="3" t="s">
+      <c r="F8" s="1">
+        <v>105</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/audio/※bgmリスト.xlsx
+++ b/audio/※bgmリスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\LS210D597\share\※２．2026年01月01日～\1．ナレッジ\０６－4.2．ClaudeCode\いしちゃんのホームページ\6516mjnt-design.github.io\audio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\LS210D597\share\※２．2026年01月01日～\1．ナレッジ\０６－4.2．ClaudeCode\6516mjnt-design.github.io_いしちゃんのホームページ\audio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C19E519-8F79-4FEA-A52D-42724CE7F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392176A5-AA1D-4F33-A0A4-AD3CB9522CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2B91B0EB-8191-4BBC-A706-21B28F855E19}"/>
+    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="13944" xr2:uid="{2B91B0EB-8191-4BBC-A706-21B28F855E19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -635,23 +635,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B01FD5-C79C-4FB1-933B-034233EA6D74}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="19.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="5.9140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.58203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.4140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.9140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.796875" style="1"/>
+    <col min="2" max="2" width="5.8984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.3984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
@@ -659,10 +659,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
@@ -679,10 +676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
@@ -696,10 +690,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
@@ -713,10 +704,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -730,10 +718,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
@@ -747,7 +732,10 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
@@ -755,7 +743,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
@@ -763,7 +754,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -771,7 +765,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -779,7 +776,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
@@ -787,7 +787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
@@ -795,7 +795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>31</v>
       </c>
@@ -803,7 +803,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
@@ -811,7 +811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
@@ -819,7 +819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
@@ -827,7 +827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>41</v>
       </c>
@@ -835,7 +835,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -843,7 +843,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -851,7 +851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
@@ -859,7 +859,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
